--- a/output/pdf_financials_xlsx/ISGI.xlsx
+++ b/output/pdf_financials_xlsx/ISGI.xlsx
@@ -1060,16 +1060,16 @@
         <v>-0.232173</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.257052</v>
+        <v>-0.257052</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.764035</v>
+        <v>-1.764035</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.43377</v>
+        <v>-0.43377</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.349075</v>
+        <v>-0.349075</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.6433179999999999</v>
@@ -1280,16 +1280,16 @@
         <v>-0.232173</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.257052</v>
+        <v>-0.257052</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.764035</v>
+        <v>-1.764035</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.43377</v>
+        <v>-0.43377</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.349075</v>
+        <v>-0.349075</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.6450129999999999</v>
@@ -1409,16 +1409,16 @@
         <v>-0.232173</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.257052</v>
+        <v>-0.257052</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.764035</v>
+        <v>-1.764035</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.43377</v>
+        <v>-0.43377</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.349075</v>
+        <v>-0.349075</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.6450129999999999</v>
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.57052</v>
+        <v>2.57052</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-6.78475</v>
+        <v>6.78475</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-8.6754</v>
+        <v>8.6754</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-11.635833</v>
+        <v>11.635833</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>14.80369</v>
@@ -1607,16 +1607,16 @@
         <v>-0.232173</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.257052</v>
+        <v>-0.257052</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.764035</v>
+        <v>-1.764035</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.43377</v>
+        <v>-0.43377</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.349075</v>
+        <v>-0.349075</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.6433179999999999</v>
@@ -1693,16 +1693,16 @@
         <v>-0.232173</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.257052</v>
+        <v>-0.257052</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.764035</v>
+        <v>-1.764035</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.43377</v>
+        <v>-0.43377</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.349075</v>
+        <v>-0.349075</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.6433179999999999</v>
@@ -1791,16 +1791,16 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0.2634777823720151</v>
@@ -4459,40 +4459,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.174004</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.174004</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.433892</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.484727</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.484727</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.226422</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.722922</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.155412</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.825001</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.839661</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.507792</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.346507</v>
       </c>
     </row>
     <row r="93">
@@ -7528,7 +7528,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10122,7 +10126,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -11708,7 +11716,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -14432,7 +14444,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -18754,7 +18770,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -19568,7 +19588,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="n">
         <v>0.174004</v>
       </c>
@@ -36399,19 +36423,19 @@
         <v>-0.232173</v>
       </c>
       <c r="F404" s="5" t="n">
-        <v>0.257052</v>
+        <v>-0.257052</v>
       </c>
       <c r="G404" s="5" t="n">
-        <v>1.764035</v>
+        <v>-1.764035</v>
       </c>
       <c r="H404" s="5" t="n">
-        <v>0.43377</v>
+        <v>-0.43377</v>
       </c>
       <c r="I404" s="5" t="n">
-        <v>0.349075</v>
+        <v>-0.349075</v>
       </c>
       <c r="J404" s="5" t="n">
-        <v>0.468958</v>
+        <v>-0.468958</v>
       </c>
       <c r="K404" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ISGI.xlsx
+++ b/output/pdf_financials_xlsx/ISGI.xlsx
@@ -885,22 +885,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002071</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000433</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000238</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000285</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000288</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000507</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1604,22 +1604,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.232173</v>
+        <v>-0.234244</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.257052</v>
+        <v>-0.256619</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.764035</v>
+        <v>-1.763797</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.43377</v>
+        <v>-0.433485</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.349075</v>
+        <v>-0.348787</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.6433179999999999</v>
+        <v>-0.642811</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-4.070069</v>
@@ -1690,22 +1690,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.232173</v>
+        <v>-0.234244</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.257052</v>
+        <v>-0.256619</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.764035</v>
+        <v>-1.763797</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.43377</v>
+        <v>-0.433485</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.349075</v>
+        <v>-0.348787</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.6433179999999999</v>
+        <v>-0.642811</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-4.070069</v>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-6361.297340057352</v>
+        <v>-6356.283990902799</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-8268.800536345536</v>
@@ -1893,40 +1893,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.041349</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.173121</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.034092</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.019219</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005172</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.215251</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.36232</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.8700059999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.567766</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.088662</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.466936</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.209703</v>
       </c>
     </row>
     <row r="35">
@@ -1979,40 +1979,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.041349</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.173121</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.034092</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.012</v>
+        <v>0.031219</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005172</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.215251</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.36232</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.8700059999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.034978</v>
+        <v>0.6027439999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.034037</v>
+        <v>0.122699</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.032968</v>
+        <v>0.499904</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.033029</v>
+        <v>0.242732</v>
       </c>
     </row>
     <row r="37">
@@ -2495,40 +2495,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.041349</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.173121</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.084092</v>
+        <v>0.05</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.019219</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005172</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.222843</v>
+        <v>0.007592</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.371288</v>
+        <v>0.008968</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.986151</v>
+        <v>0.116145</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.580658</v>
+        <v>0.012892</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.101913</v>
+        <v>0.013251</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.485147</v>
+        <v>0.018211</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.225582</v>
+        <v>0.015879</v>
       </c>
     </row>
     <row r="49">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -34706,7 +34706,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -35536,7 +35536,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -36190,7 +36190,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" s="5" t="n">

--- a/output/pdf_financials_xlsx/ISGI.xlsx
+++ b/output/pdf_financials_xlsx/ISGI.xlsx
@@ -1674,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.025062</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.025062</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.003504</v>
       </c>
     </row>
     <row r="29">
@@ -1717,13 +1717,13 @@
         <v>-1.409905</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.725961</v>
+        <v>-0.700899</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.659413</v>
+        <v>-0.634351</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.400216</v>
+        <v>-0.396712</v>
       </c>
     </row>
     <row r="30">
@@ -1770,10 +1770,10 @@
         <v>-408.4254283686505</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-107.5842047232892</v>
+        <v>-103.8701273296344</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-65.59332739815279</v>
+        <v>-63.10035262930156</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -4794,13 +4794,13 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.025062</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.025062</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.003504</v>
       </c>
     </row>
     <row r="101">
@@ -20036,7 +20036,11 @@
           <t>Amortization - intangible assets</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -31510,7 +31514,11 @@
           <t>Amortization - intangible assets 5</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ISGI.xlsx
+++ b/output/pdf_financials_xlsx/ISGI.xlsx
@@ -668,19 +668,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.148199</v>
+        <v>0.219199</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.149371</v>
+        <v>0.212371</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.207538</v>
+        <v>0.267538</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.142414</v>
+        <v>0.202414</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.119533</v>
+        <v>0.179533</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.239644</v>
@@ -3222,25 +3222,25 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.003269</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.13375</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.145331</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.15313</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.19999</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.153779</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.161903</v>
       </c>
     </row>
     <row r="65">
@@ -3351,25 +3351,25 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.032654</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.003323</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.042115</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.049052</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.048612</v>
       </c>
     </row>
     <row r="68">
@@ -5421,10 +5421,10 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.052789</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.005805</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.089125</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.027303</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
@@ -20468,7 +20468,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -22786,7 +22790,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -23160,7 +23168,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -23386,7 +23398,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -24116,7 +24132,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -29254,7 +29274,11 @@
           <t>Shares issued - private placement 1,305,000 391,500 261,000</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -35702,7 +35726,11 @@
           <t>Directors’ fees (Note 7) $</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E394" s="5" t="n">
         <v>0.07099999999999999</v>
       </c>
